--- a/ci-cd-merge-resolver/repoCollector/datasets/janusgraph.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/janusgraph.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
   <si>
     <t>mergeCommit</t>
   </si>
@@ -53,6 +53,42 @@
     <t>f44c6636c6329c5ae0edff321f999cac277b70db</t>
   </si>
   <si>
+    <t>0306efb4edbae7735fa021dd90ec979149dba175</t>
+  </si>
+  <si>
+    <t>53e23b9a5216d606727ad873ccb0632d4d860de5</t>
+  </si>
+  <si>
+    <t>7ef663f6c50e437ed6ea1772a65e2cda61eb0a7d</t>
+  </si>
+  <si>
+    <t>1943d78985cde823f86d8c48fad604d0219e8d1d</t>
+  </si>
+  <si>
+    <t>c30c7071227de338a63d82336b34f749f2384b22</t>
+  </si>
+  <si>
+    <t>50782e6c355d74c89beef3f7008afccaa7302e2d</t>
+  </si>
+  <si>
+    <t>17f3133b64b996802ea31e98aed002628c28c506</t>
+  </si>
+  <si>
+    <t>27ffe15d88db360db49fb6c6dc61b9a3b706e563</t>
+  </si>
+  <si>
+    <t>c0b8e1d77df87a394e91d06ff5d651ceea636194</t>
+  </si>
+  <si>
+    <t>59b1165b584b5f66768067e811232e9d5925c67a</t>
+  </si>
+  <si>
+    <t>6baa2765dd019b83d98524a86590c4f507f8f705</t>
+  </si>
+  <si>
+    <t>3787fd4d78d2aa5e849ea836852901b19a469ec5</t>
+  </si>
+  <si>
     <t>b9db6e8387d7aa14fbdd99b8ecfacee7569061f9</t>
   </si>
   <si>
@@ -62,31 +98,67 @@
     <t>855681621a628e18c68ddc6417daeb982e235ac1</t>
   </si>
   <si>
-    <t>569b0a2867b793f549676a80285cd742aa6b6419</t>
-  </si>
-  <si>
-    <t>97e8b22232a15b635544fe9c362b86a62f2c6a7c</t>
-  </si>
-  <si>
-    <t>a22a62e01271d1e3bdeeb6f698a3a3fed641a7c1</t>
-  </si>
-  <si>
-    <t>09ba4cf234076fd0cc0f90d2326aff0cfe096c23</t>
-  </si>
-  <si>
-    <t>a5a403fdc7b334ff9376d07b592fde7e0dabcde3</t>
-  </si>
-  <si>
-    <t>cc3915084086568b992a7d0b9ee9b1101f9d9dcb</t>
-  </si>
-  <si>
-    <t>05484fd47631c7fdcad819bcff4fbd1355838840</t>
-  </si>
-  <si>
-    <t>e257408ca31fda5d0b4c724f8ba2dbe950005c72</t>
-  </si>
-  <si>
-    <t>c1c590a78fbacf8fca30024c54b78c62ea41d533</t>
+    <t>99ee8dc64ca0a7ad58d57dc7a054ce5b47a70967</t>
+  </si>
+  <si>
+    <t>0001b013c31523b41d98636dc5a03cd42513de93</t>
+  </si>
+  <si>
+    <t>037f8af5471f5e0a2becc2cb331c822936e7d01a</t>
+  </si>
+  <si>
+    <t>176f9db0d6f4e38a5f66214de59c28874e214316</t>
+  </si>
+  <si>
+    <t>c419577576100a2014cb7fa58a95553ea50b38b2</t>
+  </si>
+  <si>
+    <t>c67a9a91756ff328ed3d9c35cfab08e84ce6f44b</t>
+  </si>
+  <si>
+    <t>1100f34a022f6db5fb5d96a344ffe24dcb4158f4</t>
+  </si>
+  <si>
+    <t>7b5b04f0faa4caba55b917e22ccb78ca23611e15</t>
+  </si>
+  <si>
+    <t>6031e745d992f5a02b093cd9af51ce37009335a5</t>
+  </si>
+  <si>
+    <t>0ea4421b2b7358f596bc17c6c39337eef5373379</t>
+  </si>
+  <si>
+    <t>b9adacf7b5819c0847f4eb1dc1f52d5b96da3190</t>
+  </si>
+  <si>
+    <t>1703e1bc7e6e7ff0074b61eb2bafb915f08b0972</t>
+  </si>
+  <si>
+    <t>6de094d9c5cb566954f9c8c595711e6b97c82701</t>
+  </si>
+  <si>
+    <t>d13cb0015705b6bd854477c303504ad496c153af</t>
+  </si>
+  <si>
+    <t>ec5d266ac401427d4520a2ac1a93a03fbc97a1f1</t>
+  </si>
+  <si>
+    <t>819ce2c90481f02492d9ebc0eaa3f667d825d246</t>
+  </si>
+  <si>
+    <t>2ffcb3bb690df2772693eb60d23a01976ae2a9f8</t>
+  </si>
+  <si>
+    <t>7cde7f83abfd43546dce428aab1506d2525c0bc0</t>
+  </si>
+  <si>
+    <t>678847fd2f6479c460434222b9ed974543f7a5f9</t>
+  </si>
+  <si>
+    <t>4f44a1db63513f01cd118b6ccbe24b5cdb36878d</t>
+  </si>
+  <si>
+    <t>39ac149c73fcacfc985485a2ac938a25e2743ce0</t>
   </si>
   <si>
     <t>b7d2c3b9efccdb2448750c8569a0c820ab616288</t>
@@ -98,42 +170,6 @@
     <t>6a483bf87024fe87f1ba3fac4216fba8f21fbf9e</t>
   </si>
   <si>
-    <t>0306efb4edbae7735fa021dd90ec979149dba175</t>
-  </si>
-  <si>
-    <t>53e23b9a5216d606727ad873ccb0632d4d860de5</t>
-  </si>
-  <si>
-    <t>7ef663f6c50e437ed6ea1772a65e2cda61eb0a7d</t>
-  </si>
-  <si>
-    <t>678847fd2f6479c460434222b9ed974543f7a5f9</t>
-  </si>
-  <si>
-    <t>4f44a1db63513f01cd118b6ccbe24b5cdb36878d</t>
-  </si>
-  <si>
-    <t>39ac149c73fcacfc985485a2ac938a25e2743ce0</t>
-  </si>
-  <si>
-    <t>59b1165b584b5f66768067e811232e9d5925c67a</t>
-  </si>
-  <si>
-    <t>6baa2765dd019b83d98524a86590c4f507f8f705</t>
-  </si>
-  <si>
-    <t>3787fd4d78d2aa5e849ea836852901b19a469ec5</t>
-  </si>
-  <si>
-    <t>1943d78985cde823f86d8c48fad604d0219e8d1d</t>
-  </si>
-  <si>
-    <t>c30c7071227de338a63d82336b34f749f2384b22</t>
-  </si>
-  <si>
-    <t>50782e6c355d74c89beef3f7008afccaa7302e2d</t>
-  </si>
-  <si>
     <t>dfac30ff7b4bbcec0b18294620462c90502c9d4d</t>
   </si>
   <si>
@@ -143,15 +179,6 @@
     <t>97adb1ff1a3fa48a72720c611a2b837626208951</t>
   </si>
   <si>
-    <t>17f3133b64b996802ea31e98aed002628c28c506</t>
-  </si>
-  <si>
-    <t>27ffe15d88db360db49fb6c6dc61b9a3b706e563</t>
-  </si>
-  <si>
-    <t>c0b8e1d77df87a394e91d06ff5d651ceea636194</t>
-  </si>
-  <si>
     <t>d361b5487258a222d479af494317c6fa614ac34e</t>
   </si>
   <si>
@@ -170,13 +197,31 @@
     <t>ee226e52415b8bf43b700afac75fa5b9767993a5</t>
   </si>
   <si>
-    <t>87f905ad3df5b7642a942db582075e6a7e098f9e</t>
-  </si>
-  <si>
-    <t>f391fb6d25dd5ba99eb9cd1faca805e70a86c719</t>
-  </si>
-  <si>
-    <t>bcf6fdbe6ee74add600151bd9403ac8940a10726</t>
+    <t>615925f05a3a25882e19e48ea45b94e955f91593</t>
+  </si>
+  <si>
+    <t>e06b8fce34449beea73422edfae2d9f822c55481</t>
+  </si>
+  <si>
+    <t>894488c5c6896fd750147820a2046cf3fd3b6258</t>
+  </si>
+  <si>
+    <t>24190f82a2a30a8f365808ccd9aa66d3ef26db7b</t>
+  </si>
+  <si>
+    <t>170833a44e2462c8425b58a93114c7171edbdaa9</t>
+  </si>
+  <si>
+    <t>1863521a2463570babb54c91e1964d07e62f8259</t>
+  </si>
+  <si>
+    <t>a4ace7b7f1cfd5ee6aaab3ba8def81c12c362527</t>
+  </si>
+  <si>
+    <t>a7bb8e7eb030bd9c9de860094d8db1ddc766a4d5</t>
+  </si>
+  <si>
+    <t>630d2c03b519c8c9b4bc90bcb6488683f49f1642</t>
   </si>
   <si>
     <t>4ac4a63d3d15c02e30847794d9625e382b2e7d1c</t>
@@ -188,15 +233,6 @@
     <t>71ad7a6d8bfc4d09d0be15865d3ad166893a0ee6</t>
   </si>
   <si>
-    <t>24190f82a2a30a8f365808ccd9aa66d3ef26db7b</t>
-  </si>
-  <si>
-    <t>170833a44e2462c8425b58a93114c7171edbdaa9</t>
-  </si>
-  <si>
-    <t>1863521a2463570babb54c91e1964d07e62f8259</t>
-  </si>
-  <si>
     <t>32bbec6de962a953c06a850d4e8f7b222b3d4045</t>
   </si>
   <si>
@@ -204,114 +240,6 @@
   </si>
   <si>
     <t>6cb92e9c33ad6f113ce0ff6db96dd0a52d05d1ca</t>
-  </si>
-  <si>
-    <t>1100f34a022f6db5fb5d96a344ffe24dcb4158f4</t>
-  </si>
-  <si>
-    <t>7b5b04f0faa4caba55b917e22ccb78ca23611e15</t>
-  </si>
-  <si>
-    <t>6031e745d992f5a02b093cd9af51ce37009335a5</t>
-  </si>
-  <si>
-    <t>6de094d9c5cb566954f9c8c595711e6b97c82701</t>
-  </si>
-  <si>
-    <t>d13cb0015705b6bd854477c303504ad496c153af</t>
-  </si>
-  <si>
-    <t>ec5d266ac401427d4520a2ac1a93a03fbc97a1f1</t>
-  </si>
-  <si>
-    <t>0ea4421b2b7358f596bc17c6c39337eef5373379</t>
-  </si>
-  <si>
-    <t>b9adacf7b5819c0847f4eb1dc1f52d5b96da3190</t>
-  </si>
-  <si>
-    <t>1703e1bc7e6e7ff0074b61eb2bafb915f08b0972</t>
-  </si>
-  <si>
-    <t>615925f05a3a25882e19e48ea45b94e955f91593</t>
-  </si>
-  <si>
-    <t>e06b8fce34449beea73422edfae2d9f822c55481</t>
-  </si>
-  <si>
-    <t>894488c5c6896fd750147820a2046cf3fd3b6258</t>
-  </si>
-  <si>
-    <t>99ee8dc64ca0a7ad58d57dc7a054ce5b47a70967</t>
-  </si>
-  <si>
-    <t>0001b013c31523b41d98636dc5a03cd42513de93</t>
-  </si>
-  <si>
-    <t>037f8af5471f5e0a2becc2cb331c822936e7d01a</t>
-  </si>
-  <si>
-    <t>819ce2c90481f02492d9ebc0eaa3f667d825d246</t>
-  </si>
-  <si>
-    <t>2ffcb3bb690df2772693eb60d23a01976ae2a9f8</t>
-  </si>
-  <si>
-    <t>7cde7f83abfd43546dce428aab1506d2525c0bc0</t>
-  </si>
-  <si>
-    <t>a4ace7b7f1cfd5ee6aaab3ba8def81c12c362527</t>
-  </si>
-  <si>
-    <t>a7bb8e7eb030bd9c9de860094d8db1ddc766a4d5</t>
-  </si>
-  <si>
-    <t>630d2c03b519c8c9b4bc90bcb6488683f49f1642</t>
-  </si>
-  <si>
-    <t>176f9db0d6f4e38a5f66214de59c28874e214316</t>
-  </si>
-  <si>
-    <t>c419577576100a2014cb7fa58a95553ea50b38b2</t>
-  </si>
-  <si>
-    <t>c67a9a91756ff328ed3d9c35cfab08e84ce6f44b</t>
-  </si>
-  <si>
-    <t>1b3e8d864c5f5af0d56388894e2bba0e79ddee22</t>
-  </si>
-  <si>
-    <t>d2aa2ee911e22b96b762a27b181a3695f14ae9e6</t>
-  </si>
-  <si>
-    <t>32073687f68ec47085fea9194626bd2c9358f2e9</t>
-  </si>
-  <si>
-    <t>1a3b58809aaf980948663224a844ec9680db3618</t>
-  </si>
-  <si>
-    <t>e768a1597b5338710538b4d243446343136eeb20</t>
-  </si>
-  <si>
-    <t>eab1b24fb6cb1fa875990b9809554766327c5afa</t>
-  </si>
-  <si>
-    <t>be17a5deb678c864d837c1bab5fa5d2f79c3197d</t>
-  </si>
-  <si>
-    <t>b22bf6da38557e12393315627e2d01509738f3e5</t>
-  </si>
-  <si>
-    <t>fbe83c6023c321420bb8f768bf3e72e5eca7e684</t>
-  </si>
-  <si>
-    <t>5e336911c905a4241c356337a3c30fbd9ad97df3</t>
-  </si>
-  <si>
-    <t>ced2cee93f2f3e7259e78ada4648566d49db95ee</t>
-  </si>
-  <si>
-    <t>cacc6fba6a13273e3e64de3de09a197b6fa436a8</t>
   </si>
 </sst>
 </file>
@@ -356,7 +284,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -402,7 +330,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>76.0</v>
+        <v>81.0</v>
       </c>
       <c r="E2" t="n" s="0">
         <v>1.0</v>
@@ -417,10 +345,10 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>24.51599884033203</v>
+        <v>2.180000066757202</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -434,10 +362,10 @@
         <v>15</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>67.0</v>
+        <v>81.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="F3" t="n" s="0">
         <v>1.0</v>
@@ -449,10 +377,10 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>19.768001556396484</v>
+        <v>2.752999782562256</v>
       </c>
       <c r="J3" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -466,13 +394,13 @@
         <v>18</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>67.0</v>
+        <v>87.0</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="F4" t="n" s="0">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G4" t="b" s="0">
         <v>0</v>
@@ -481,10 +409,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>15.72900104522705</v>
+        <v>2.937999963760376</v>
       </c>
       <c r="J4" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -498,13 +426,13 @@
         <v>21</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>16.0</v>
+        <v>697.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G5" t="b" s="0">
         <v>0</v>
@@ -513,10 +441,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>5.246999740600586</v>
+        <v>406.65399169921875</v>
       </c>
       <c r="J5" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -530,13 +458,13 @@
         <v>24</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>16.0</v>
+        <v>74.0</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G6" t="b" s="0">
         <v>0</v>
@@ -545,10 +473,10 @@
         <v>1</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>6.383999824523926</v>
+        <v>2.8409998416900635</v>
       </c>
       <c r="J6" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -562,7 +490,7 @@
         <v>27</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>67.0</v>
+        <v>74.0</v>
       </c>
       <c r="E7" t="n" s="0">
         <v>1.0</v>
@@ -577,10 +505,10 @@
         <v>1</v>
       </c>
       <c r="I7" t="n" s="0">
-        <v>10.569000244140625</v>
+        <v>2.234999895095825</v>
       </c>
       <c r="J7" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -594,13 +522,13 @@
         <v>30</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>76.0</v>
+        <v>553.0</v>
       </c>
       <c r="E8" t="n" s="0">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
       <c r="F8" t="n" s="0">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
       <c r="G8" t="b" s="0">
         <v>0</v>
@@ -609,10 +537,10 @@
         <v>1</v>
       </c>
       <c r="I8" t="n" s="0">
-        <v>17.661001205444336</v>
+        <v>701.4740600585938</v>
       </c>
       <c r="J8" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -626,13 +554,13 @@
         <v>33</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>67.0</v>
+        <v>524.0</v>
       </c>
       <c r="E9" t="n" s="0">
-        <v>2.0</v>
+        <v>13.0</v>
       </c>
       <c r="F9" t="n" s="0">
-        <v>2.0</v>
+        <v>12.0</v>
       </c>
       <c r="G9" t="b" s="0">
         <v>0</v>
@@ -641,10 +569,10 @@
         <v>1</v>
       </c>
       <c r="I9" t="n" s="0">
-        <v>14.512001037597656</v>
+        <v>722.7171020507812</v>
       </c>
       <c r="J9" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -658,13 +586,13 @@
         <v>36</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>67.0</v>
+        <v>553.0</v>
       </c>
       <c r="E10" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="F10" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G10" t="b" s="0">
         <v>0</v>
@@ -673,10 +601,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="n" s="0">
-        <v>17.66900062561035</v>
+        <v>718.5540771484375</v>
       </c>
       <c r="J10" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -690,13 +618,13 @@
         <v>39</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>82.0</v>
+        <v>569.0</v>
       </c>
       <c r="E11" t="n" s="0">
-        <v>2.0</v>
+        <v>37.0</v>
       </c>
       <c r="F11" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G11" t="b" s="0">
         <v>0</v>
@@ -705,10 +633,10 @@
         <v>1</v>
       </c>
       <c r="I11" t="n" s="0">
-        <v>25.769001007080078</v>
+        <v>719.9930419921875</v>
       </c>
       <c r="J11" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -722,13 +650,13 @@
         <v>42</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>143.0</v>
+        <v>557.0</v>
       </c>
       <c r="E12" t="n" s="0">
-        <v>8.0</v>
+        <v>36.0</v>
       </c>
       <c r="F12" t="n" s="0">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="G12" t="b" s="0">
         <v>0</v>
@@ -737,10 +665,10 @@
         <v>1</v>
       </c>
       <c r="I12" t="n" s="0">
-        <v>506.6349792480469</v>
+        <v>712.1990356445312</v>
       </c>
       <c r="J12" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -754,13 +682,13 @@
         <v>45</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>325.0</v>
+        <v>572.0</v>
       </c>
       <c r="E13" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="F13" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G13" t="b" s="0">
         <v>0</v>
@@ -769,10 +697,10 @@
         <v>1</v>
       </c>
       <c r="I13" t="n" s="0">
-        <v>367.35504150390625</v>
+        <v>714.02099609375</v>
       </c>
       <c r="J13" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -786,13 +714,13 @@
         <v>48</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>221.0</v>
+        <v>72.0</v>
       </c>
       <c r="E14" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="F14" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G14" t="b" s="0">
         <v>0</v>
@@ -801,10 +729,10 @@
         <v>1</v>
       </c>
       <c r="I14" t="n" s="0">
-        <v>671.9949951171875</v>
+        <v>1.7559999227523804</v>
       </c>
       <c r="J14" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -818,13 +746,13 @@
         <v>51</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>178.0</v>
+        <v>72.0</v>
       </c>
       <c r="E15" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="F15" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G15" t="b" s="0">
         <v>0</v>
@@ -833,10 +761,10 @@
         <v>1</v>
       </c>
       <c r="I15" t="n" s="0">
-        <v>632.7460327148438</v>
+        <v>1.6660000085830688</v>
       </c>
       <c r="J15" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -850,13 +778,13 @@
         <v>54</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>296.0</v>
+        <v>356.0</v>
       </c>
       <c r="E16" t="n" s="0">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="F16" t="n" s="0">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="G16" t="b" s="0">
         <v>0</v>
@@ -865,10 +793,10 @@
         <v>1</v>
       </c>
       <c r="I16" t="n" s="0">
-        <v>682.0790405273438</v>
+        <v>427.94403076171875</v>
       </c>
       <c r="J16" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -882,13 +810,13 @@
         <v>57</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>257.0</v>
+        <v>276.0</v>
       </c>
       <c r="E17" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="F17" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G17" t="b" s="0">
         <v>0</v>
@@ -897,10 +825,10 @@
         <v>1</v>
       </c>
       <c r="I17" t="n" s="0">
-        <v>663.9349365234375</v>
+        <v>528.4790649414062</v>
       </c>
       <c r="J17" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -914,13 +842,13 @@
         <v>60</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>259.0</v>
+        <v>382.0</v>
       </c>
       <c r="E18" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F18" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G18" t="b" s="0">
         <v>0</v>
@@ -929,10 +857,10 @@
         <v>1</v>
       </c>
       <c r="I18" t="n" s="0">
-        <v>652.2329711914062</v>
+        <v>677.4380493164062</v>
       </c>
       <c r="J18" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -946,13 +874,13 @@
         <v>63</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>259.0</v>
+        <v>483.0</v>
       </c>
       <c r="E19" t="n" s="0">
         <v>2.0</v>
       </c>
       <c r="F19" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G19" t="b" s="0">
         <v>0</v>
@@ -961,10 +889,10 @@
         <v>1</v>
       </c>
       <c r="I19" t="n" s="0">
-        <v>658.5709228515625</v>
+        <v>716.6420288085938</v>
       </c>
       <c r="J19" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -978,10 +906,10 @@
         <v>66</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>291.0</v>
+        <v>483.0</v>
       </c>
       <c r="E20" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F20" t="n" s="0">
         <v>1.0</v>
@@ -993,10 +921,10 @@
         <v>1</v>
       </c>
       <c r="I20" t="n" s="0">
-        <v>682.6619262695312</v>
+        <v>709.9891357421875</v>
       </c>
       <c r="J20" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1010,13 +938,13 @@
         <v>69</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>293.0</v>
+        <v>5.0</v>
       </c>
       <c r="E21" t="n" s="0">
-        <v>36.0</v>
+        <v>40.0</v>
       </c>
       <c r="F21" t="n" s="0">
-        <v>1.0</v>
+        <v>35.0</v>
       </c>
       <c r="G21" t="b" s="0">
         <v>0</v>
@@ -1025,10 +953,10 @@
         <v>1</v>
       </c>
       <c r="I21" t="n" s="0">
-        <v>685.9871215820312</v>
+        <v>600.4600219726562</v>
       </c>
       <c r="J21" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1042,13 +970,13 @@
         <v>72</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>294.0</v>
+        <v>445.0</v>
       </c>
       <c r="E22" t="n" s="0">
-        <v>37.0</v>
+        <v>2.0</v>
       </c>
       <c r="F22" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G22" t="b" s="0">
         <v>0</v>
@@ -1057,10 +985,10 @@
         <v>1</v>
       </c>
       <c r="I22" t="n" s="0">
-        <v>693.9530029296875</v>
+        <v>505.93896484375</v>
       </c>
       <c r="J22" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1074,13 +1002,13 @@
         <v>75</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>259.0</v>
+        <v>447.0</v>
       </c>
       <c r="E23" t="n" s="0">
         <v>2.0</v>
       </c>
       <c r="F23" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G23" t="b" s="0">
         <v>0</v>
@@ -1089,266 +1017,10 @@
         <v>1</v>
       </c>
       <c r="I23" t="n" s="0">
-        <v>654.751953125</v>
+        <v>518.22998046875</v>
       </c>
       <c r="J23" t="b" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="0">
-        <v>76</v>
-      </c>
-      <c r="B24" t="s" s="0">
-        <v>77</v>
-      </c>
-      <c r="C24" t="s" s="0">
-        <v>78</v>
-      </c>
-      <c r="D24" t="n" s="0">
-        <v>291.0</v>
-      </c>
-      <c r="E24" t="n" s="0">
-        <v>14.0</v>
-      </c>
-      <c r="F24" t="n" s="0">
-        <v>13.0</v>
-      </c>
-      <c r="G24" t="b" s="0">
-        <v>0</v>
-      </c>
-      <c r="H24" t="b" s="0">
-        <v>1</v>
-      </c>
-      <c r="I24" t="n" s="0">
-        <v>672.6979370117188</v>
-      </c>
-      <c r="J24" t="b" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="0">
-        <v>79</v>
-      </c>
-      <c r="B25" t="s" s="0">
-        <v>80</v>
-      </c>
-      <c r="C25" t="s" s="0">
-        <v>81</v>
-      </c>
-      <c r="D25" t="n" s="0">
-        <v>296.0</v>
-      </c>
-      <c r="E25" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="F25" t="n" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="G25" t="b" s="0">
-        <v>0</v>
-      </c>
-      <c r="H25" t="b" s="0">
-        <v>1</v>
-      </c>
-      <c r="I25" t="n" s="0">
-        <v>680.3399658203125</v>
-      </c>
-      <c r="J25" t="b" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="0">
-        <v>82</v>
-      </c>
-      <c r="B26" t="s" s="0">
-        <v>83</v>
-      </c>
-      <c r="C26" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="D26" t="n" s="0">
-        <v>236.0</v>
-      </c>
-      <c r="E26" t="n" s="0">
-        <v>40.0</v>
-      </c>
-      <c r="F26" t="n" s="0">
-        <v>35.0</v>
-      </c>
-      <c r="G26" t="b" s="0">
-        <v>0</v>
-      </c>
-      <c r="H26" t="b" s="0">
-        <v>1</v>
-      </c>
-      <c r="I26" t="n" s="0">
-        <v>615.9600219726562</v>
-      </c>
-      <c r="J26" t="b" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="0">
-        <v>85</v>
-      </c>
-      <c r="B27" t="s" s="0">
-        <v>86</v>
-      </c>
-      <c r="C27" t="s" s="0">
-        <v>87</v>
-      </c>
-      <c r="D27" t="n" s="0">
-        <v>262.0</v>
-      </c>
-      <c r="E27" t="n" s="0">
-        <v>13.0</v>
-      </c>
-      <c r="F27" t="n" s="0">
-        <v>12.0</v>
-      </c>
-      <c r="G27" t="b" s="0">
-        <v>0</v>
-      </c>
-      <c r="H27" t="b" s="0">
-        <v>1</v>
-      </c>
-      <c r="I27" t="n" s="0">
-        <v>667.5060424804688</v>
-      </c>
-      <c r="J27" t="b" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="0">
-        <v>88</v>
-      </c>
-      <c r="B28" t="s" s="0">
-        <v>89</v>
-      </c>
-      <c r="C28" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="D28" t="n" s="0">
-        <v>327.0</v>
-      </c>
-      <c r="E28" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="F28" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G28" t="b" s="0">
-        <v>0</v>
-      </c>
-      <c r="H28" t="b" s="0">
-        <v>1</v>
-      </c>
-      <c r="I28" t="n" s="0">
-        <v>691.9119873046875</v>
-      </c>
-      <c r="J28" t="b" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="B29" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="C29" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="D29" t="n" s="0">
-        <v>330.0</v>
-      </c>
-      <c r="E29" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="F29" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G29" t="b" s="0">
-        <v>0</v>
-      </c>
-      <c r="H29" t="b" s="0">
-        <v>1</v>
-      </c>
-      <c r="I29" t="n" s="0">
-        <v>697.057861328125</v>
-      </c>
-      <c r="J29" t="b" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="0">
-        <v>94</v>
-      </c>
-      <c r="B30" t="s" s="0">
-        <v>95</v>
-      </c>
-      <c r="C30" t="s" s="0">
-        <v>96</v>
-      </c>
-      <c r="D30" t="n" s="0">
-        <v>328.0</v>
-      </c>
-      <c r="E30" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="F30" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G30" t="b" s="0">
-        <v>0</v>
-      </c>
-      <c r="H30" t="b" s="0">
-        <v>1</v>
-      </c>
-      <c r="I30" t="n" s="0">
-        <v>680.2479248046875</v>
-      </c>
-      <c r="J30" t="b" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="0">
-        <v>97</v>
-      </c>
-      <c r="B31" t="s" s="0">
-        <v>98</v>
-      </c>
-      <c r="C31" t="s" s="0">
-        <v>99</v>
-      </c>
-      <c r="D31" t="n" s="0">
-        <v>354.0</v>
-      </c>
-      <c r="E31" t="n" s="0">
-        <v>147.0</v>
-      </c>
-      <c r="F31" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G31" t="b" s="0">
-        <v>0</v>
-      </c>
-      <c r="H31" t="b" s="0">
-        <v>1</v>
-      </c>
-      <c r="I31" t="n" s="0">
-        <v>695.1009521484375</v>
-      </c>
-      <c r="J31" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
